--- a/data/labour-market/Employment rate/employment_rate_trends_10022026.xlsx
+++ b/data/labour-market/Employment rate/employment_rate_trends_10022026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10201"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/files/IPR/Centres/Brunel Centre/Labour Market/Employment_rate/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="X:\IPR\Centres\Brunel Centre\Labour Market\Employment_rate\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5BC3D5C-0FD0-F741-9B46-BD131BB4B338}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D474F24-E40F-458E-BC7A-A8BB08AD892E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="32340" yWindow="-21100" windowWidth="38400" windowHeight="21100" activeTab="2" xr2:uid="{F3838E48-33B6-3E4D-ABD2-7FEC8AC3400F}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{F3838E48-33B6-3E4D-ABD2-7FEC8AC3400F}"/>
   </bookViews>
   <sheets>
     <sheet name="Metadata" sheetId="2" r:id="rId1"/>
@@ -89,9 +89,6 @@
   </si>
   <si>
     <t>Office for National Statistics (ONS)</t>
-  </si>
-  <si>
-    <t>The Greater West of England Area (Bristol, Bath &amp; North East Somerset, South Gloucestershire, North Somerset, Swindon, Wiltshire) and individual local authorities, England and United Kingdom (+excluding London)</t>
   </si>
   <si>
     <t>Aggregated by NOMIS</t>
@@ -321,6 +318,9 @@
   <si>
     <t>A residence based labour market survey encompassing population, economic activity (employment and unemployment), economic inactivity and qualifications. These are broken down where possible by gender, age, ethnicity, industry and occupation. Available at Local Authority level and above. Updated quarterly.</t>
   </si>
+  <si>
+    <t>The Greater West of England Area (Bristol, Bath &amp; North East Somerset, South Gloucestershire, North Somerset, Swindon, Wiltshire, Gloucestershire) and individual local authorities, England and United Kingdom (+excluding London)</t>
+  </si>
 </sst>
 </file>
 
@@ -392,7 +392,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -424,6 +424,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -760,13 +763,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF34F89D-D895-144E-9321-FCBFF913ABF8}">
   <dimension ref="A1:B11"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="16" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="19.5" customWidth="1"/>
     <col min="2" max="2" width="54.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>5</v>
       </c>
@@ -774,28 +777,28 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A4" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A5" s="1" t="s">
         <v>9</v>
       </c>
@@ -803,15 +806,15 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A6" s="1" t="s">
         <v>10</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A7" s="1" t="s">
         <v>11</v>
       </c>
@@ -819,34 +822,34 @@
         <v>46063</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A8" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B8" s="2"/>
     </row>
-    <row r="9" spans="1:2" ht="32" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:2" ht="64" x14ac:dyDescent="0.4">
       <c r="A9" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B9" s="15" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A10" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="80" x14ac:dyDescent="0.4">
       <c r="A11" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B11" t="s">
-        <v>93</v>
+      <c r="B11" s="15" t="s">
+        <v>92</v>
       </c>
     </row>
   </sheetData>
@@ -857,326 +860,326 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{43F31F01-CF34-B04B-8F44-AFC33149FAE8}">
   <dimension ref="A1:BI106"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1" collapsed="1"/>
     <col min="2" max="61" width="14" customWidth="1" collapsed="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:61" x14ac:dyDescent="0.4">
       <c r="A1" s="3" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="2" spans="1:61" x14ac:dyDescent="0.4">
+      <c r="A2" s="4" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="2" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A2" s="4" t="s">
+    <row r="4" spans="1:61" x14ac:dyDescent="0.4">
+      <c r="A4" s="5" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="4" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A4" s="5" t="s">
+      <c r="B4" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="B4" s="5" t="s">
+    </row>
+    <row r="5" spans="1:61" x14ac:dyDescent="0.4">
+      <c r="A5" s="5" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="5" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A5" s="5" t="s">
+      <c r="B5" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="B5" s="5" t="s">
+    </row>
+    <row r="6" spans="1:61" x14ac:dyDescent="0.4">
+      <c r="A6" s="5" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="6" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A6" s="5" t="s">
+      <c r="B6" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="B6" s="5" t="s">
+    </row>
+    <row r="8" spans="1:61" ht="26" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" s="13" t="s">
         <v>70</v>
-      </c>
-    </row>
-    <row r="8" spans="1:61" ht="26" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="B8" s="13" t="s">
-        <v>71</v>
       </c>
       <c r="C8" s="14"/>
       <c r="D8" s="14"/>
       <c r="E8" s="14"/>
       <c r="F8" s="13" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G8" s="14"/>
       <c r="H8" s="14"/>
       <c r="I8" s="14"/>
       <c r="J8" s="13" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K8" s="14"/>
       <c r="L8" s="14"/>
       <c r="M8" s="14"/>
       <c r="N8" s="13" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="O8" s="14"/>
       <c r="P8" s="14"/>
       <c r="Q8" s="14"/>
       <c r="R8" s="13" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="S8" s="14"/>
       <c r="T8" s="14"/>
       <c r="U8" s="14"/>
       <c r="V8" s="13" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="W8" s="14"/>
       <c r="X8" s="14"/>
       <c r="Y8" s="14"/>
       <c r="Z8" s="13" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AA8" s="14"/>
       <c r="AB8" s="14"/>
       <c r="AC8" s="14"/>
       <c r="AD8" s="13" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AE8" s="14"/>
       <c r="AF8" s="14"/>
       <c r="AG8" s="14"/>
       <c r="AH8" s="13" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AI8" s="14"/>
       <c r="AJ8" s="14"/>
       <c r="AK8" s="14"/>
       <c r="AL8" s="13" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AM8" s="14"/>
       <c r="AN8" s="14"/>
       <c r="AO8" s="14"/>
       <c r="AP8" s="13" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AQ8" s="14"/>
       <c r="AR8" s="14"/>
       <c r="AS8" s="14"/>
       <c r="AT8" s="13" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="AU8" s="14"/>
       <c r="AV8" s="14"/>
       <c r="AW8" s="14"/>
       <c r="AX8" s="13" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AY8" s="14"/>
       <c r="AZ8" s="14"/>
       <c r="BA8" s="14"/>
       <c r="BB8" s="13" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="BC8" s="14"/>
       <c r="BD8" s="14"/>
       <c r="BE8" s="14"/>
       <c r="BF8" s="13" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="BG8" s="14"/>
       <c r="BH8" s="14"/>
       <c r="BI8" s="14"/>
     </row>
-    <row r="9" spans="1:61" ht="26" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:61" ht="26" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B9" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="C9" s="9" t="s">
+      <c r="D9" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="D9" s="9" t="s">
+      <c r="E9" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="E9" s="9" t="s">
-        <v>25</v>
-      </c>
       <c r="F9" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="G9" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="G9" s="9" t="s">
+      <c r="H9" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="H9" s="9" t="s">
+      <c r="I9" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="I9" s="9" t="s">
-        <v>25</v>
-      </c>
       <c r="J9" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="K9" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="K9" s="9" t="s">
+      <c r="L9" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="L9" s="9" t="s">
+      <c r="M9" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="M9" s="9" t="s">
-        <v>25</v>
-      </c>
       <c r="N9" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="O9" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="O9" s="9" t="s">
+      <c r="P9" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="P9" s="9" t="s">
+      <c r="Q9" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="Q9" s="9" t="s">
-        <v>25</v>
-      </c>
       <c r="R9" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="S9" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="S9" s="9" t="s">
+      <c r="T9" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="T9" s="9" t="s">
+      <c r="U9" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="U9" s="9" t="s">
-        <v>25</v>
-      </c>
       <c r="V9" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="W9" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="W9" s="9" t="s">
+      <c r="X9" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="X9" s="9" t="s">
+      <c r="Y9" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="Y9" s="9" t="s">
-        <v>25</v>
-      </c>
       <c r="Z9" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="AA9" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="AA9" s="9" t="s">
+      <c r="AB9" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="AB9" s="9" t="s">
+      <c r="AC9" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="AC9" s="9" t="s">
-        <v>25</v>
-      </c>
       <c r="AD9" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="AE9" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="AE9" s="9" t="s">
+      <c r="AF9" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="AF9" s="9" t="s">
+      <c r="AG9" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="AG9" s="9" t="s">
-        <v>25</v>
-      </c>
       <c r="AH9" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="AI9" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="AI9" s="9" t="s">
+      <c r="AJ9" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="AJ9" s="9" t="s">
+      <c r="AK9" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="AK9" s="9" t="s">
-        <v>25</v>
-      </c>
       <c r="AL9" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="AM9" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="AM9" s="9" t="s">
+      <c r="AN9" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="AN9" s="9" t="s">
+      <c r="AO9" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="AO9" s="9" t="s">
-        <v>25</v>
-      </c>
       <c r="AP9" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="AQ9" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="AQ9" s="9" t="s">
+      <c r="AR9" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="AR9" s="9" t="s">
+      <c r="AS9" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="AS9" s="9" t="s">
-        <v>25</v>
-      </c>
       <c r="AT9" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="AU9" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="AU9" s="9" t="s">
+      <c r="AV9" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="AV9" s="9" t="s">
+      <c r="AW9" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="AW9" s="9" t="s">
-        <v>25</v>
-      </c>
       <c r="AX9" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="AY9" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="AY9" s="9" t="s">
+      <c r="AZ9" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="AZ9" s="9" t="s">
+      <c r="BA9" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="BA9" s="9" t="s">
-        <v>25</v>
-      </c>
       <c r="BB9" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="BC9" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="BC9" s="9" t="s">
+      <c r="BD9" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="BD9" s="9" t="s">
+      <c r="BE9" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="BE9" s="9" t="s">
-        <v>25</v>
-      </c>
       <c r="BF9" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="BG9" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="BG9" s="9" t="s">
+      <c r="BH9" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="BH9" s="9" t="s">
+      <c r="BI9" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="BI9" s="9" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="10" spans="1:61" x14ac:dyDescent="0.2">
+    </row>
+    <row r="10" spans="1:61" x14ac:dyDescent="0.4">
       <c r="A10" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B10" s="7">
         <v>1097400</v>
@@ -1359,9 +1362,9 @@
         <v>3.3</v>
       </c>
     </row>
-    <row r="11" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:61" x14ac:dyDescent="0.4">
       <c r="A11" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B11" s="7">
         <v>1120400</v>
@@ -1544,9 +1547,9 @@
         <v>4.0999999999999996</v>
       </c>
     </row>
-    <row r="12" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:61" x14ac:dyDescent="0.4">
       <c r="A12" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B12" s="7">
         <v>1137200</v>
@@ -1729,9 +1732,9 @@
         <v>3.9</v>
       </c>
     </row>
-    <row r="13" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:61" x14ac:dyDescent="0.4">
       <c r="A13" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B13" s="7">
         <v>1149400</v>
@@ -1914,9 +1917,9 @@
         <v>3.8</v>
       </c>
     </row>
-    <row r="14" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:61" x14ac:dyDescent="0.4">
       <c r="A14" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B14" s="7">
         <v>1128200</v>
@@ -2099,9 +2102,9 @@
         <v>4.0999999999999996</v>
       </c>
     </row>
-    <row r="15" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:61" x14ac:dyDescent="0.4">
       <c r="A15" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B15" s="7">
         <v>1125300</v>
@@ -2284,9 +2287,9 @@
         <v>4.5</v>
       </c>
     </row>
-    <row r="16" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:61" x14ac:dyDescent="0.4">
       <c r="A16" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B16" s="7">
         <v>1126300</v>
@@ -2469,9 +2472,9 @@
         <v>4.7</v>
       </c>
     </row>
-    <row r="17" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:61" x14ac:dyDescent="0.4">
       <c r="A17" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B17" s="7">
         <v>1108600</v>
@@ -2654,9 +2657,9 @@
         <v>4.8</v>
       </c>
     </row>
-    <row r="18" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:61" x14ac:dyDescent="0.4">
       <c r="A18" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B18" s="7">
         <v>1115300</v>
@@ -2839,9 +2842,9 @@
         <v>4.5</v>
       </c>
     </row>
-    <row r="19" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:61" x14ac:dyDescent="0.4">
       <c r="A19" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B19" s="7">
         <v>1136600</v>
@@ -3024,9 +3027,9 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="20" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:61" x14ac:dyDescent="0.4">
       <c r="A20" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B20" s="7">
         <v>1180300</v>
@@ -3209,9 +3212,9 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="21" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:61" x14ac:dyDescent="0.4">
       <c r="A21" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B21" s="7">
         <v>1201200</v>
@@ -3394,9 +3397,9 @@
         <v>4.5</v>
       </c>
     </row>
-    <row r="22" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:61" x14ac:dyDescent="0.4">
       <c r="A22" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B22" s="7">
         <v>1218700</v>
@@ -3579,9 +3582,9 @@
         <v>4.5</v>
       </c>
     </row>
-    <row r="23" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:61" x14ac:dyDescent="0.4">
       <c r="A23" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B23" s="7">
         <v>1229300</v>
@@ -3764,9 +3767,9 @@
         <v>4.5</v>
       </c>
     </row>
-    <row r="24" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:61" x14ac:dyDescent="0.4">
       <c r="A24" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B24" s="7">
         <v>1230600</v>
@@ -3949,9 +3952,9 @@
         <v>4.9000000000000004</v>
       </c>
     </row>
-    <row r="25" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:61" x14ac:dyDescent="0.4">
       <c r="A25" s="5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B25" s="7">
         <v>1233900</v>
@@ -4134,9 +4137,9 @@
         <v>5.2</v>
       </c>
     </row>
-    <row r="26" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:61" x14ac:dyDescent="0.4">
       <c r="A26" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B26" s="7">
         <v>1211600</v>
@@ -4319,9 +4322,9 @@
         <v>5.3</v>
       </c>
     </row>
-    <row r="27" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:61" x14ac:dyDescent="0.4">
       <c r="A27" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B27" s="7">
         <v>1252600</v>
@@ -4504,9 +4507,9 @@
         <v>5.6</v>
       </c>
     </row>
-    <row r="28" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:61" x14ac:dyDescent="0.4">
       <c r="A28" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B28" s="7">
         <v>1240200</v>
@@ -4689,9 +4692,9 @@
         <v>6.7</v>
       </c>
     </row>
-    <row r="29" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:61" x14ac:dyDescent="0.4">
       <c r="A29" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B29" s="7">
         <v>1262400</v>
@@ -4874,9 +4877,9 @@
         <v>6.2</v>
       </c>
     </row>
-    <row r="30" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:61" x14ac:dyDescent="0.4">
       <c r="A30" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B30" s="7">
         <v>1264300</v>
@@ -5059,335 +5062,335 @@
         <v>6</v>
       </c>
     </row>
-    <row r="32" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:61" x14ac:dyDescent="0.4">
       <c r="A32" s="4" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="33" spans="1:61" x14ac:dyDescent="0.4">
+      <c r="A33" s="4" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="33" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A33" s="4" t="s">
+    <row r="34" spans="1:61" x14ac:dyDescent="0.4">
+      <c r="A34" s="4" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="34" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A34" s="4" t="s">
+    <row r="37" spans="1:61" x14ac:dyDescent="0.4">
+      <c r="A37" s="3" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="38" spans="1:61" x14ac:dyDescent="0.4">
+      <c r="A38" s="4" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="40" spans="1:61" x14ac:dyDescent="0.4">
+      <c r="A40" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="41" spans="1:61" x14ac:dyDescent="0.4">
+      <c r="A41" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="42" spans="1:61" x14ac:dyDescent="0.4">
+      <c r="A42" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="B42" s="5" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="37" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A37" s="3" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="38" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A38" s="4" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="40" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A40" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="41" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A41" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="B41" s="5" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="42" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A42" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="44" spans="1:61" ht="26" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:61" ht="26" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A44" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B44" s="13" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C44" s="14"/>
       <c r="D44" s="14"/>
       <c r="E44" s="14"/>
       <c r="F44" s="13" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G44" s="14"/>
       <c r="H44" s="14"/>
       <c r="I44" s="14"/>
       <c r="J44" s="13" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K44" s="14"/>
       <c r="L44" s="14"/>
       <c r="M44" s="14"/>
       <c r="N44" s="13" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="O44" s="14"/>
       <c r="P44" s="14"/>
       <c r="Q44" s="14"/>
       <c r="R44" s="13" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="S44" s="14"/>
       <c r="T44" s="14"/>
       <c r="U44" s="14"/>
       <c r="V44" s="13" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="W44" s="14"/>
       <c r="X44" s="14"/>
       <c r="Y44" s="14"/>
       <c r="Z44" s="13" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AA44" s="14"/>
       <c r="AB44" s="14"/>
       <c r="AC44" s="14"/>
       <c r="AD44" s="13" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AE44" s="14"/>
       <c r="AF44" s="14"/>
       <c r="AG44" s="14"/>
       <c r="AH44" s="13" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AI44" s="14"/>
       <c r="AJ44" s="14"/>
       <c r="AK44" s="14"/>
       <c r="AL44" s="13" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AM44" s="14"/>
       <c r="AN44" s="14"/>
       <c r="AO44" s="14"/>
       <c r="AP44" s="13" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AQ44" s="14"/>
       <c r="AR44" s="14"/>
       <c r="AS44" s="14"/>
       <c r="AT44" s="13" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="AU44" s="14"/>
       <c r="AV44" s="14"/>
       <c r="AW44" s="14"/>
       <c r="AX44" s="13" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AY44" s="14"/>
       <c r="AZ44" s="14"/>
       <c r="BA44" s="14"/>
       <c r="BB44" s="13" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="BC44" s="14"/>
       <c r="BD44" s="14"/>
       <c r="BE44" s="14"/>
       <c r="BF44" s="13" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="BG44" s="14"/>
       <c r="BH44" s="14"/>
       <c r="BI44" s="14"/>
     </row>
-    <row r="45" spans="1:61" ht="26" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:61" ht="26" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B45" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="C45" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="C45" s="9" t="s">
+      <c r="D45" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="D45" s="9" t="s">
+      <c r="E45" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="E45" s="9" t="s">
-        <v>25</v>
-      </c>
       <c r="F45" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="G45" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="G45" s="9" t="s">
+      <c r="H45" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="H45" s="9" t="s">
+      <c r="I45" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="I45" s="9" t="s">
-        <v>25</v>
-      </c>
       <c r="J45" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="K45" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="K45" s="9" t="s">
+      <c r="L45" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="L45" s="9" t="s">
+      <c r="M45" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="M45" s="9" t="s">
-        <v>25</v>
-      </c>
       <c r="N45" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="O45" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="O45" s="9" t="s">
+      <c r="P45" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="P45" s="9" t="s">
+      <c r="Q45" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="Q45" s="9" t="s">
-        <v>25</v>
-      </c>
       <c r="R45" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="S45" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="S45" s="9" t="s">
+      <c r="T45" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="T45" s="9" t="s">
+      <c r="U45" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="U45" s="9" t="s">
-        <v>25</v>
-      </c>
       <c r="V45" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="W45" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="W45" s="9" t="s">
+      <c r="X45" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="X45" s="9" t="s">
+      <c r="Y45" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="Y45" s="9" t="s">
-        <v>25</v>
-      </c>
       <c r="Z45" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="AA45" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="AA45" s="9" t="s">
+      <c r="AB45" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="AB45" s="9" t="s">
+      <c r="AC45" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="AC45" s="9" t="s">
-        <v>25</v>
-      </c>
       <c r="AD45" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="AE45" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="AE45" s="9" t="s">
+      <c r="AF45" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="AF45" s="9" t="s">
+      <c r="AG45" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="AG45" s="9" t="s">
-        <v>25</v>
-      </c>
       <c r="AH45" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="AI45" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="AI45" s="9" t="s">
+      <c r="AJ45" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="AJ45" s="9" t="s">
+      <c r="AK45" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="AK45" s="9" t="s">
-        <v>25</v>
-      </c>
       <c r="AL45" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="AM45" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="AM45" s="9" t="s">
+      <c r="AN45" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="AN45" s="9" t="s">
+      <c r="AO45" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="AO45" s="9" t="s">
-        <v>25</v>
-      </c>
       <c r="AP45" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="AQ45" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="AQ45" s="9" t="s">
+      <c r="AR45" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="AR45" s="9" t="s">
+      <c r="AS45" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="AS45" s="9" t="s">
-        <v>25</v>
-      </c>
       <c r="AT45" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="AU45" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="AU45" s="9" t="s">
+      <c r="AV45" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="AV45" s="9" t="s">
+      <c r="AW45" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="AW45" s="9" t="s">
-        <v>25</v>
-      </c>
       <c r="AX45" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="AY45" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="AY45" s="9" t="s">
+      <c r="AZ45" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="AZ45" s="9" t="s">
+      <c r="BA45" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="BA45" s="9" t="s">
-        <v>25</v>
-      </c>
       <c r="BB45" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="BC45" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="BC45" s="9" t="s">
+      <c r="BD45" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="BD45" s="9" t="s">
+      <c r="BE45" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="BE45" s="9" t="s">
-        <v>25</v>
-      </c>
       <c r="BF45" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="BG45" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="BG45" s="9" t="s">
+      <c r="BH45" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="BH45" s="9" t="s">
+      <c r="BI45" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="BI45" s="9" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="46" spans="1:61" x14ac:dyDescent="0.2">
+    </row>
+    <row r="46" spans="1:61" x14ac:dyDescent="0.4">
       <c r="A46" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B46" s="7">
         <v>27956900</v>
@@ -5570,9 +5573,9 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="47" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:61" x14ac:dyDescent="0.4">
       <c r="A47" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B47" s="7">
         <v>28188800</v>
@@ -5755,9 +5758,9 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="48" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:61" x14ac:dyDescent="0.4">
       <c r="A48" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B48" s="7">
         <v>28518300</v>
@@ -5940,9 +5943,9 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="49" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:61" x14ac:dyDescent="0.4">
       <c r="A49" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B49" s="7">
         <v>28794600</v>
@@ -6125,9 +6128,9 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="50" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:61" x14ac:dyDescent="0.4">
       <c r="A50" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B50" s="7">
         <v>28475000</v>
@@ -6310,9 +6313,9 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="51" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:61" x14ac:dyDescent="0.4">
       <c r="A51" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B51" s="7">
         <v>28195000</v>
@@ -6495,9 +6498,9 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="52" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:61" x14ac:dyDescent="0.4">
       <c r="A52" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B52" s="7">
         <v>28294300</v>
@@ -6680,9 +6683,9 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="53" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:61" x14ac:dyDescent="0.4">
       <c r="A53" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B53" s="7">
         <v>28383200</v>
@@ -6865,9 +6868,9 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="54" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:61" x14ac:dyDescent="0.4">
       <c r="A54" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B54" s="7">
         <v>28678300</v>
@@ -7050,9 +7053,9 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="55" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:61" x14ac:dyDescent="0.4">
       <c r="A55" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B55" s="7">
         <v>29120300</v>
@@ -7235,9 +7238,9 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="56" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:61" x14ac:dyDescent="0.4">
       <c r="A56" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B56" s="7">
         <v>29705300</v>
@@ -7420,9 +7423,9 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="57" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:61" x14ac:dyDescent="0.4">
       <c r="A57" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B57" s="7">
         <v>30159700</v>
@@ -7605,9 +7608,9 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="58" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:61" x14ac:dyDescent="0.4">
       <c r="A58" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B58" s="7">
         <v>30500100</v>
@@ -7790,9 +7793,9 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="59" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:61" x14ac:dyDescent="0.4">
       <c r="A59" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B59" s="7">
         <v>30842800</v>
@@ -7975,9 +7978,9 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="60" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:61" x14ac:dyDescent="0.4">
       <c r="A60" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B60" s="7">
         <v>31161400</v>
@@ -8160,9 +8163,9 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="61" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:61" x14ac:dyDescent="0.4">
       <c r="A61" s="5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B61" s="7">
         <v>31351400</v>
@@ -8345,9 +8348,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:61" x14ac:dyDescent="0.4">
       <c r="A62" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B62" s="7">
         <v>30729900</v>
@@ -8530,9 +8533,9 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="63" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:61" x14ac:dyDescent="0.4">
       <c r="A63" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B63" s="7">
         <v>31230700</v>
@@ -8715,9 +8718,9 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="64" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:61" x14ac:dyDescent="0.4">
       <c r="A64" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B64" s="7">
         <v>31405800</v>
@@ -8900,9 +8903,9 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="65" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:61" x14ac:dyDescent="0.4">
       <c r="A65" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B65" s="7">
         <v>31447200</v>
@@ -9085,9 +9088,9 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="66" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:61" x14ac:dyDescent="0.4">
       <c r="A66" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B66" s="7">
         <v>31631100</v>
@@ -9270,335 +9273,335 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="68" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:61" x14ac:dyDescent="0.4">
       <c r="A68" s="4" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="69" spans="1:61" x14ac:dyDescent="0.4">
+      <c r="A69" s="4" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="69" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A69" s="4" t="s">
+    <row r="70" spans="1:61" x14ac:dyDescent="0.4">
+      <c r="A70" s="4" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="70" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A70" s="4" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="73" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:61" x14ac:dyDescent="0.4">
       <c r="A73" s="3" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="74" spans="1:61" x14ac:dyDescent="0.4">
+      <c r="A74" s="4" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="74" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A74" s="4" t="s">
+    <row r="76" spans="1:61" x14ac:dyDescent="0.4">
+      <c r="A76" s="5" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="76" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A76" s="5" t="s">
+      <c r="B76" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="B76" s="5" t="s">
+    </row>
+    <row r="77" spans="1:61" x14ac:dyDescent="0.4">
+      <c r="A77" s="5" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="77" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A77" s="5" t="s">
+      <c r="B77" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="B77" s="5" t="s">
+    </row>
+    <row r="78" spans="1:61" x14ac:dyDescent="0.4">
+      <c r="A78" s="5" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="78" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A78" s="5" t="s">
-        <v>69</v>
-      </c>
       <c r="B78" s="5" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="80" spans="1:61" ht="26" customHeight="1" x14ac:dyDescent="0.2">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="80" spans="1:61" ht="26" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A80" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B80" s="13" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C80" s="14"/>
       <c r="D80" s="14"/>
       <c r="E80" s="14"/>
       <c r="F80" s="13" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G80" s="14"/>
       <c r="H80" s="14"/>
       <c r="I80" s="14"/>
       <c r="J80" s="13" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K80" s="14"/>
       <c r="L80" s="14"/>
       <c r="M80" s="14"/>
       <c r="N80" s="13" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="O80" s="14"/>
       <c r="P80" s="14"/>
       <c r="Q80" s="14"/>
       <c r="R80" s="13" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="S80" s="14"/>
       <c r="T80" s="14"/>
       <c r="U80" s="14"/>
       <c r="V80" s="13" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="W80" s="14"/>
       <c r="X80" s="14"/>
       <c r="Y80" s="14"/>
       <c r="Z80" s="13" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AA80" s="14"/>
       <c r="AB80" s="14"/>
       <c r="AC80" s="14"/>
       <c r="AD80" s="13" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AE80" s="14"/>
       <c r="AF80" s="14"/>
       <c r="AG80" s="14"/>
       <c r="AH80" s="13" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AI80" s="14"/>
       <c r="AJ80" s="14"/>
       <c r="AK80" s="14"/>
       <c r="AL80" s="13" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AM80" s="14"/>
       <c r="AN80" s="14"/>
       <c r="AO80" s="14"/>
       <c r="AP80" s="13" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AQ80" s="14"/>
       <c r="AR80" s="14"/>
       <c r="AS80" s="14"/>
       <c r="AT80" s="13" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="AU80" s="14"/>
       <c r="AV80" s="14"/>
       <c r="AW80" s="14"/>
       <c r="AX80" s="13" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AY80" s="14"/>
       <c r="AZ80" s="14"/>
       <c r="BA80" s="14"/>
       <c r="BB80" s="13" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="BC80" s="14"/>
       <c r="BD80" s="14"/>
       <c r="BE80" s="14"/>
       <c r="BF80" s="13" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="BG80" s="14"/>
       <c r="BH80" s="14"/>
       <c r="BI80" s="14"/>
     </row>
-    <row r="81" spans="1:61" ht="26" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:61" ht="26" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B81" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="C81" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="C81" s="9" t="s">
+      <c r="D81" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="D81" s="9" t="s">
+      <c r="E81" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="E81" s="9" t="s">
-        <v>25</v>
-      </c>
       <c r="F81" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="G81" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="G81" s="9" t="s">
+      <c r="H81" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="H81" s="9" t="s">
+      <c r="I81" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="I81" s="9" t="s">
-        <v>25</v>
-      </c>
       <c r="J81" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="K81" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="K81" s="9" t="s">
+      <c r="L81" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="L81" s="9" t="s">
+      <c r="M81" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="M81" s="9" t="s">
-        <v>25</v>
-      </c>
       <c r="N81" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="O81" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="O81" s="9" t="s">
+      <c r="P81" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="P81" s="9" t="s">
+      <c r="Q81" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="Q81" s="9" t="s">
-        <v>25</v>
-      </c>
       <c r="R81" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="S81" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="S81" s="9" t="s">
+      <c r="T81" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="T81" s="9" t="s">
+      <c r="U81" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="U81" s="9" t="s">
-        <v>25</v>
-      </c>
       <c r="V81" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="W81" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="W81" s="9" t="s">
+      <c r="X81" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="X81" s="9" t="s">
+      <c r="Y81" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="Y81" s="9" t="s">
-        <v>25</v>
-      </c>
       <c r="Z81" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="AA81" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="AA81" s="9" t="s">
+      <c r="AB81" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="AB81" s="9" t="s">
+      <c r="AC81" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="AC81" s="9" t="s">
-        <v>25</v>
-      </c>
       <c r="AD81" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="AE81" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="AE81" s="9" t="s">
+      <c r="AF81" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="AF81" s="9" t="s">
+      <c r="AG81" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="AG81" s="9" t="s">
-        <v>25</v>
-      </c>
       <c r="AH81" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="AI81" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="AI81" s="9" t="s">
+      <c r="AJ81" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="AJ81" s="9" t="s">
+      <c r="AK81" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="AK81" s="9" t="s">
-        <v>25</v>
-      </c>
       <c r="AL81" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="AM81" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="AM81" s="9" t="s">
+      <c r="AN81" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="AN81" s="9" t="s">
+      <c r="AO81" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="AO81" s="9" t="s">
-        <v>25</v>
-      </c>
       <c r="AP81" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="AQ81" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="AQ81" s="9" t="s">
+      <c r="AR81" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="AR81" s="9" t="s">
+      <c r="AS81" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="AS81" s="9" t="s">
-        <v>25</v>
-      </c>
       <c r="AT81" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="AU81" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="AU81" s="9" t="s">
+      <c r="AV81" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="AV81" s="9" t="s">
+      <c r="AW81" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="AW81" s="9" t="s">
-        <v>25</v>
-      </c>
       <c r="AX81" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="AY81" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="AY81" s="9" t="s">
+      <c r="AZ81" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="AZ81" s="9" t="s">
+      <c r="BA81" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="BA81" s="9" t="s">
-        <v>25</v>
-      </c>
       <c r="BB81" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="BC81" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="BC81" s="9" t="s">
+      <c r="BD81" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="BD81" s="9" t="s">
+      <c r="BE81" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="BE81" s="9" t="s">
-        <v>25</v>
-      </c>
       <c r="BF81" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="BG81" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="BG81" s="9" t="s">
+      <c r="BH81" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="BH81" s="9" t="s">
+      <c r="BI81" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="BI81" s="9" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="82" spans="1:61" x14ac:dyDescent="0.2">
+    </row>
+    <row r="82" spans="1:61" x14ac:dyDescent="0.4">
       <c r="A82" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B82" s="7">
         <v>24513500</v>
@@ -9781,9 +9784,9 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="83" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:61" x14ac:dyDescent="0.4">
       <c r="A83" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B83" s="7">
         <v>24703200</v>
@@ -9966,9 +9969,9 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="84" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:61" x14ac:dyDescent="0.4">
       <c r="A84" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B84" s="7">
         <v>24942900</v>
@@ -10151,9 +10154,9 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="85" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:61" x14ac:dyDescent="0.4">
       <c r="A85" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B85" s="7">
         <v>25116000</v>
@@ -10336,9 +10339,9 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="86" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:61" x14ac:dyDescent="0.4">
       <c r="A86" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B86" s="7">
         <v>24808000</v>
@@ -10521,9 +10524,9 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="87" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:61" x14ac:dyDescent="0.4">
       <c r="A87" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B87" s="7">
         <v>24486500</v>
@@ -10706,9 +10709,9 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="88" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:61" x14ac:dyDescent="0.4">
       <c r="A88" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B88" s="7">
         <v>24540800</v>
@@ -10891,9 +10894,9 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="89" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:61" x14ac:dyDescent="0.4">
       <c r="A89" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B89" s="7">
         <v>24580000</v>
@@ -11076,9 +11079,9 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="90" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:61" x14ac:dyDescent="0.4">
       <c r="A90" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B90" s="7">
         <v>24761800</v>
@@ -11261,9 +11264,9 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="91" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:61" x14ac:dyDescent="0.4">
       <c r="A91" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B91" s="7">
         <v>25049000</v>
@@ -11446,9 +11449,9 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="92" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:61" x14ac:dyDescent="0.4">
       <c r="A92" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B92" s="7">
         <v>25493800</v>
@@ -11631,9 +11634,9 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="93" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:61" x14ac:dyDescent="0.4">
       <c r="A93" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B93" s="7">
         <v>25847700</v>
@@ -11816,9 +11819,9 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="94" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:61" x14ac:dyDescent="0.4">
       <c r="A94" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B94" s="7">
         <v>26132200</v>
@@ -12001,9 +12004,9 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="95" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:61" x14ac:dyDescent="0.4">
       <c r="A95" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B95" s="7">
         <v>26405500</v>
@@ -12186,9 +12189,9 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="96" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:61" x14ac:dyDescent="0.4">
       <c r="A96" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B96" s="7">
         <v>26659800</v>
@@ -12371,9 +12374,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:61" x14ac:dyDescent="0.4">
       <c r="A97" s="5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B97" s="7">
         <v>26769600</v>
@@ -12556,9 +12559,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:61" x14ac:dyDescent="0.4">
       <c r="A98" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B98" s="7">
         <v>26207400</v>
@@ -12741,9 +12744,9 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="99" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:61" x14ac:dyDescent="0.4">
       <c r="A99" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B99" s="7">
         <v>26572800</v>
@@ -12926,9 +12929,9 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="100" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:61" x14ac:dyDescent="0.4">
       <c r="A100" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B100" s="7">
         <v>26771200</v>
@@ -13111,9 +13114,9 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="101" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:61" x14ac:dyDescent="0.4">
       <c r="A101" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B101" s="7">
         <v>26794700</v>
@@ -13296,9 +13299,9 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="102" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:61" x14ac:dyDescent="0.4">
       <c r="A102" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B102" s="7">
         <v>26941500</v>
@@ -13481,29 +13484,46 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="104" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:61" x14ac:dyDescent="0.4">
       <c r="A104" s="4" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="105" spans="1:61" x14ac:dyDescent="0.4">
+      <c r="A105" s="4" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="105" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A105" s="4" t="s">
+    <row r="106" spans="1:61" x14ac:dyDescent="0.4">
+      <c r="A106" s="4" t="s">
         <v>87</v>
-      </c>
-    </row>
-    <row r="106" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A106" s="4" t="s">
-        <v>88</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="45">
-    <mergeCell ref="V8:Y8"/>
-    <mergeCell ref="B8:E8"/>
-    <mergeCell ref="F8:I8"/>
-    <mergeCell ref="J8:M8"/>
-    <mergeCell ref="N8:Q8"/>
-    <mergeCell ref="R8:U8"/>
+    <mergeCell ref="BF80:BI80"/>
+    <mergeCell ref="AH80:AK80"/>
+    <mergeCell ref="AL80:AO80"/>
+    <mergeCell ref="AP80:AS80"/>
+    <mergeCell ref="AT80:AW80"/>
+    <mergeCell ref="AX80:BA80"/>
+    <mergeCell ref="BB80:BE80"/>
+    <mergeCell ref="BB44:BE44"/>
+    <mergeCell ref="BF44:BI44"/>
+    <mergeCell ref="B80:E80"/>
+    <mergeCell ref="F80:I80"/>
+    <mergeCell ref="J80:M80"/>
+    <mergeCell ref="N80:Q80"/>
+    <mergeCell ref="R80:U80"/>
+    <mergeCell ref="V80:Y80"/>
+    <mergeCell ref="Z80:AC80"/>
+    <mergeCell ref="AD80:AG80"/>
+    <mergeCell ref="AD44:AG44"/>
+    <mergeCell ref="AH44:AK44"/>
+    <mergeCell ref="AL44:AO44"/>
+    <mergeCell ref="AP44:AS44"/>
+    <mergeCell ref="AT44:AW44"/>
+    <mergeCell ref="AX44:BA44"/>
     <mergeCell ref="AX8:BA8"/>
     <mergeCell ref="BB8:BE8"/>
     <mergeCell ref="BF8:BI8"/>
@@ -13520,29 +13540,12 @@
     <mergeCell ref="AL8:AO8"/>
     <mergeCell ref="AP8:AS8"/>
     <mergeCell ref="AT8:AW8"/>
-    <mergeCell ref="BB44:BE44"/>
-    <mergeCell ref="BF44:BI44"/>
-    <mergeCell ref="B80:E80"/>
-    <mergeCell ref="F80:I80"/>
-    <mergeCell ref="J80:M80"/>
-    <mergeCell ref="N80:Q80"/>
-    <mergeCell ref="R80:U80"/>
-    <mergeCell ref="V80:Y80"/>
-    <mergeCell ref="Z80:AC80"/>
-    <mergeCell ref="AD80:AG80"/>
-    <mergeCell ref="AD44:AG44"/>
-    <mergeCell ref="AH44:AK44"/>
-    <mergeCell ref="AL44:AO44"/>
-    <mergeCell ref="AP44:AS44"/>
-    <mergeCell ref="AT44:AW44"/>
-    <mergeCell ref="AX44:BA44"/>
-    <mergeCell ref="BF80:BI80"/>
-    <mergeCell ref="AH80:AK80"/>
-    <mergeCell ref="AL80:AO80"/>
-    <mergeCell ref="AP80:AS80"/>
-    <mergeCell ref="AT80:AW80"/>
-    <mergeCell ref="AX80:BA80"/>
-    <mergeCell ref="BB80:BE80"/>
+    <mergeCell ref="V8:Y8"/>
+    <mergeCell ref="B8:E8"/>
+    <mergeCell ref="F8:I8"/>
+    <mergeCell ref="J8:M8"/>
+    <mergeCell ref="N8:Q8"/>
+    <mergeCell ref="R8:U8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -13551,7 +13554,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EDBF1B92-E1FB-E74A-B3FF-5116134587D5}">
   <dimension ref="A1:V64"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="16" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="32" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.6640625" bestFit="1" customWidth="1"/>
@@ -13564,24 +13567,24 @@
     <col min="10" max="10" width="13.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C1" t="s">
         <v>21</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>22</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>23</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>24</v>
-      </c>
-      <c r="F1" t="s">
-        <v>25</v>
       </c>
       <c r="G1" t="s">
         <v>1</v>
@@ -13590,54 +13593,54 @@
         <v>2</v>
       </c>
       <c r="I1" t="s">
+        <v>25</v>
+      </c>
+      <c r="J1" t="s">
         <v>26</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>27</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>28</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>29</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>30</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>31</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>32</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>33</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>34</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" t="s">
         <v>35</v>
       </c>
-      <c r="S1" t="s">
+      <c r="T1" t="s">
         <v>36</v>
       </c>
-      <c r="T1" t="s">
+      <c r="U1" t="s">
         <v>37</v>
       </c>
-      <c r="U1" t="s">
+      <c r="V1" t="s">
         <v>38</v>
       </c>
-      <c r="V1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="2" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A2" s="2">
         <v>38504</v>
       </c>
       <c r="B2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C2">
         <v>1097400</v>
@@ -13652,7 +13655,7 @@
         <v>0.8</v>
       </c>
       <c r="G2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H2" t="s">
         <v>3</v>
@@ -13700,12 +13703,12 @@
         <v>68.8</v>
       </c>
     </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A3" s="2">
         <v>38869</v>
       </c>
       <c r="B3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C3">
         <v>1120400</v>
@@ -13720,7 +13723,7 @@
         <v>1</v>
       </c>
       <c r="G3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H3" t="s">
         <v>3</v>
@@ -13768,12 +13771,12 @@
         <v>71.599999999999994</v>
       </c>
     </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A4" s="2">
         <v>39234</v>
       </c>
       <c r="B4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C4">
         <v>1137200</v>
@@ -13788,7 +13791,7 @@
         <v>0.9</v>
       </c>
       <c r="G4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H4" t="s">
         <v>3</v>
@@ -13836,12 +13839,12 @@
         <v>71.400000000000006</v>
       </c>
     </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A5" s="2">
         <v>39600</v>
       </c>
       <c r="B5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C5">
         <v>1149400</v>
@@ -13856,7 +13859,7 @@
         <v>1</v>
       </c>
       <c r="G5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H5" t="s">
         <v>3</v>
@@ -13904,12 +13907,12 @@
         <v>70.900000000000006</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A6" s="2">
         <v>39965</v>
       </c>
       <c r="B6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C6">
         <v>1128200</v>
@@ -13924,7 +13927,7 @@
         <v>1</v>
       </c>
       <c r="G6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H6" t="s">
         <v>3</v>
@@ -13972,12 +13975,12 @@
         <v>71.7</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A7" s="2">
         <v>40330</v>
       </c>
       <c r="B7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C7">
         <v>1125300</v>
@@ -13992,7 +13995,7 @@
         <v>1</v>
       </c>
       <c r="G7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H7" t="s">
         <v>3</v>
@@ -14040,12 +14043,12 @@
         <v>70.5</v>
       </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A8" s="2">
         <v>40695</v>
       </c>
       <c r="B8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C8">
         <v>1126300</v>
@@ -14060,7 +14063,7 @@
         <v>1.1000000000000001</v>
       </c>
       <c r="G8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H8" t="s">
         <v>3</v>
@@ -14108,12 +14111,12 @@
         <v>69.7</v>
       </c>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A9" s="2">
         <v>41061</v>
       </c>
       <c r="B9" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C9">
         <v>1108600</v>
@@ -14128,7 +14131,7 @@
         <v>1.1000000000000001</v>
       </c>
       <c r="G9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H9" t="s">
         <v>3</v>
@@ -14176,12 +14179,12 @@
         <v>69.2</v>
       </c>
     </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A10" s="2">
         <v>41426</v>
       </c>
       <c r="B10" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C10">
         <v>1115300</v>
@@ -14196,7 +14199,7 @@
         <v>1.1000000000000001</v>
       </c>
       <c r="G10" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H10" t="s">
         <v>3</v>
@@ -14244,12 +14247,12 @@
         <v>70</v>
       </c>
     </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A11" s="2">
         <v>41791</v>
       </c>
       <c r="B11" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C11">
         <v>1136600</v>
@@ -14264,7 +14267,7 @@
         <v>1</v>
       </c>
       <c r="G11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H11" t="s">
         <v>3</v>
@@ -14312,12 +14315,12 @@
         <v>72.599999999999994</v>
       </c>
     </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A12" s="2">
         <v>42156</v>
       </c>
       <c r="B12" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C12">
         <v>1180300</v>
@@ -14332,7 +14335,7 @@
         <v>1</v>
       </c>
       <c r="G12" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H12" t="s">
         <v>3</v>
@@ -14380,12 +14383,12 @@
         <v>74.5</v>
       </c>
     </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A13" s="2">
         <v>42522</v>
       </c>
       <c r="B13" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C13">
         <v>1201200</v>
@@ -14400,7 +14403,7 @@
         <v>1</v>
       </c>
       <c r="G13" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H13" t="s">
         <v>3</v>
@@ -14448,12 +14451,12 @@
         <v>74.400000000000006</v>
       </c>
     </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A14" s="2">
         <v>42887</v>
       </c>
       <c r="B14" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C14">
         <v>1218700</v>
@@ -14468,7 +14471,7 @@
         <v>1</v>
       </c>
       <c r="G14" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H14" t="s">
         <v>3</v>
@@ -14516,12 +14519,12 @@
         <v>77.099999999999994</v>
       </c>
     </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A15" s="2">
         <v>43252</v>
       </c>
       <c r="B15" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C15">
         <v>1229300</v>
@@ -14536,7 +14539,7 @@
         <v>1</v>
       </c>
       <c r="G15" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H15" t="s">
         <v>3</v>
@@ -14584,12 +14587,12 @@
         <v>75.8</v>
       </c>
     </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A16" s="2">
         <v>43617</v>
       </c>
       <c r="B16" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C16">
         <v>1230600</v>
@@ -14604,7 +14607,7 @@
         <v>1</v>
       </c>
       <c r="G16" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H16" t="s">
         <v>3</v>
@@ -14652,12 +14655,12 @@
         <v>76.599999999999994</v>
       </c>
     </row>
-    <row r="17" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A17" s="2">
         <v>43983</v>
       </c>
       <c r="B17" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C17">
         <v>1233900</v>
@@ -14672,7 +14675,7 @@
         <v>1.1000000000000001</v>
       </c>
       <c r="G17" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H17" t="s">
         <v>3</v>
@@ -14720,12 +14723,12 @@
         <v>77.099999999999994</v>
       </c>
     </row>
-    <row r="18" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A18" s="2">
         <v>44348</v>
       </c>
       <c r="B18" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C18">
         <v>1211600</v>
@@ -14740,7 +14743,7 @@
         <v>1.1000000000000001</v>
       </c>
       <c r="G18" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H18" t="s">
         <v>3</v>
@@ -14788,12 +14791,12 @@
         <v>75.5</v>
       </c>
     </row>
-    <row r="19" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A19" s="2">
         <v>44713</v>
       </c>
       <c r="B19" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C19">
         <v>1252600</v>
@@ -14808,7 +14811,7 @@
         <v>1.1000000000000001</v>
       </c>
       <c r="G19" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H19" t="s">
         <v>3</v>
@@ -14856,12 +14859,12 @@
         <v>75.599999999999994</v>
       </c>
     </row>
-    <row r="20" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A20" s="2">
         <v>45078</v>
       </c>
       <c r="B20" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C20">
         <v>1240200</v>
@@ -14876,7 +14879,7 @@
         <v>1.3</v>
       </c>
       <c r="G20" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H20" t="s">
         <v>3</v>
@@ -14924,12 +14927,12 @@
         <v>75.099999999999994</v>
       </c>
     </row>
-    <row r="21" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A21" s="2">
         <v>45444</v>
       </c>
       <c r="B21" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C21">
         <v>1262400</v>
@@ -14944,7 +14947,7 @@
         <v>1.3</v>
       </c>
       <c r="G21" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H21" t="s">
         <v>3</v>
@@ -14992,12 +14995,12 @@
         <v>75.099999999999994</v>
       </c>
     </row>
-    <row r="22" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A22" s="2">
         <v>45809</v>
       </c>
       <c r="B22" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C22">
         <v>1264300</v>
@@ -15012,7 +15015,7 @@
         <v>1.2</v>
       </c>
       <c r="G22" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H22" t="s">
         <v>3</v>
@@ -15060,12 +15063,12 @@
         <v>76.2</v>
       </c>
     </row>
-    <row r="23" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A23" s="2">
         <v>38504</v>
       </c>
       <c r="B23" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C23">
         <v>24513500</v>
@@ -15080,7 +15083,7 @@
         <v>0.2</v>
       </c>
       <c r="G23" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="H23" t="s">
         <v>4</v>
@@ -15128,12 +15131,12 @@
         <v>64.099999999999994</v>
       </c>
     </row>
-    <row r="24" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A24" s="2">
         <v>38869</v>
       </c>
       <c r="B24" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C24">
         <v>24703200</v>
@@ -15148,7 +15151,7 @@
         <v>0.2</v>
       </c>
       <c r="G24" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="H24" t="s">
         <v>4</v>
@@ -15196,12 +15199,12 @@
         <v>64.8</v>
       </c>
     </row>
-    <row r="25" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A25" s="2">
         <v>39234</v>
       </c>
       <c r="B25" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C25">
         <v>24942900</v>
@@ -15216,7 +15219,7 @@
         <v>0.2</v>
       </c>
       <c r="G25" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="H25" t="s">
         <v>4</v>
@@ -15264,12 +15267,12 @@
         <v>64.8</v>
       </c>
     </row>
-    <row r="26" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A26" s="2">
         <v>39600</v>
       </c>
       <c r="B26" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C26">
         <v>25116000</v>
@@ -15284,7 +15287,7 @@
         <v>0.2</v>
       </c>
       <c r="G26" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="H26" t="s">
         <v>4</v>
@@ -15332,12 +15335,12 @@
         <v>65</v>
       </c>
     </row>
-    <row r="27" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A27" s="2">
         <v>39965</v>
       </c>
       <c r="B27" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C27">
         <v>24808000</v>
@@ -15352,7 +15355,7 @@
         <v>0.2</v>
       </c>
       <c r="G27" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="H27" t="s">
         <v>4</v>
@@ -15400,12 +15403,12 @@
         <v>64.900000000000006</v>
       </c>
     </row>
-    <row r="28" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A28" s="2">
         <v>40330</v>
       </c>
       <c r="B28" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C28">
         <v>24486500</v>
@@ -15420,7 +15423,7 @@
         <v>0.2</v>
       </c>
       <c r="G28" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="H28" t="s">
         <v>4</v>
@@ -15468,12 +15471,12 @@
         <v>64.599999999999994</v>
       </c>
     </row>
-    <row r="29" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A29" s="2">
         <v>40695</v>
       </c>
       <c r="B29" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C29">
         <v>24540800</v>
@@ -15488,7 +15491,7 @@
         <v>0.2</v>
       </c>
       <c r="G29" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="H29" t="s">
         <v>4</v>
@@ -15536,12 +15539,12 @@
         <v>64.5</v>
       </c>
     </row>
-    <row r="30" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A30" s="2">
         <v>41061</v>
       </c>
       <c r="B30" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C30">
         <v>24580000</v>
@@ -15556,7 +15559,7 @@
         <v>0.2</v>
       </c>
       <c r="G30" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="H30" t="s">
         <v>4</v>
@@ -15604,12 +15607,12 @@
         <v>65</v>
       </c>
     </row>
-    <row r="31" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A31" s="2">
         <v>41426</v>
       </c>
       <c r="B31" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C31">
         <v>24761800</v>
@@ -15624,7 +15627,7 @@
         <v>0.2</v>
       </c>
       <c r="G31" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="H31" t="s">
         <v>4</v>
@@ -15672,12 +15675,12 @@
         <v>66.5</v>
       </c>
     </row>
-    <row r="32" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A32" s="2">
         <v>41791</v>
       </c>
       <c r="B32" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C32">
         <v>25049000</v>
@@ -15692,7 +15695,7 @@
         <v>0.2</v>
       </c>
       <c r="G32" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="H32" t="s">
         <v>4</v>
@@ -15740,12 +15743,12 @@
         <v>67.7</v>
       </c>
     </row>
-    <row r="33" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A33" s="2">
         <v>42156</v>
       </c>
       <c r="B33" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C33">
         <v>25493800</v>
@@ -15760,7 +15763,7 @@
         <v>0.2</v>
       </c>
       <c r="G33" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="H33" t="s">
         <v>4</v>
@@ -15808,12 +15811,12 @@
         <v>68.8</v>
       </c>
     </row>
-    <row r="34" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A34" s="2">
         <v>42522</v>
       </c>
       <c r="B34" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C34">
         <v>25847700</v>
@@ -15828,7 +15831,7 @@
         <v>0.2</v>
       </c>
       <c r="G34" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="H34" t="s">
         <v>4</v>
@@ -15876,12 +15879,12 @@
         <v>69.8</v>
       </c>
     </row>
-    <row r="35" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A35" s="2">
         <v>42887</v>
       </c>
       <c r="B35" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C35">
         <v>26132200</v>
@@ -15896,7 +15899,7 @@
         <v>0.2</v>
       </c>
       <c r="G35" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="H35" t="s">
         <v>4</v>
@@ -15944,12 +15947,12 @@
         <v>70.3</v>
       </c>
     </row>
-    <row r="36" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A36" s="2">
         <v>43252</v>
       </c>
       <c r="B36" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C36">
         <v>26405500</v>
@@ -15964,7 +15967,7 @@
         <v>0.2</v>
       </c>
       <c r="G36" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="H36" t="s">
         <v>4</v>
@@ -16012,12 +16015,12 @@
         <v>70.900000000000006</v>
       </c>
     </row>
-    <row r="37" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A37" s="2">
         <v>43617</v>
       </c>
       <c r="B37" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C37">
         <v>26659800</v>
@@ -16032,7 +16035,7 @@
         <v>0.2</v>
       </c>
       <c r="G37" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="H37" t="s">
         <v>4</v>
@@ -16080,12 +16083,12 @@
         <v>72</v>
       </c>
     </row>
-    <row r="38" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A38" s="2">
         <v>43983</v>
       </c>
       <c r="B38" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C38">
         <v>26769600</v>
@@ -16100,7 +16103,7 @@
         <v>0.2</v>
       </c>
       <c r="G38" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="H38" t="s">
         <v>4</v>
@@ -16148,12 +16151,12 @@
         <v>72.2</v>
       </c>
     </row>
-    <row r="39" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A39" s="2">
         <v>44348</v>
       </c>
       <c r="B39" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C39">
         <v>26207400</v>
@@ -16168,7 +16171,7 @@
         <v>0.3</v>
       </c>
       <c r="G39" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="H39" t="s">
         <v>4</v>
@@ -16216,12 +16219,12 @@
         <v>70.599999999999994</v>
       </c>
     </row>
-    <row r="40" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A40" s="2">
         <v>44713</v>
       </c>
       <c r="B40" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C40">
         <v>26572800</v>
@@ -16236,7 +16239,7 @@
         <v>0.3</v>
       </c>
       <c r="G40" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="H40" t="s">
         <v>4</v>
@@ -16284,12 +16287,12 @@
         <v>70.599999999999994</v>
       </c>
     </row>
-    <row r="41" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A41" s="2">
         <v>45078</v>
       </c>
       <c r="B41" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C41">
         <v>26771200</v>
@@ -16304,7 +16307,7 @@
         <v>0.3</v>
       </c>
       <c r="G41" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="H41" t="s">
         <v>4</v>
@@ -16352,12 +16355,12 @@
         <v>71.2</v>
       </c>
     </row>
-    <row r="42" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A42" s="2">
         <v>45444</v>
       </c>
       <c r="B42" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C42">
         <v>26794700</v>
@@ -16372,7 +16375,7 @@
         <v>0.3</v>
       </c>
       <c r="G42" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="H42" t="s">
         <v>4</v>
@@ -16420,12 +16423,12 @@
         <v>71.2</v>
       </c>
     </row>
-    <row r="43" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A43" s="2">
         <v>45809</v>
       </c>
       <c r="B43" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C43">
         <v>26941500</v>
@@ -16440,7 +16443,7 @@
         <v>0.3</v>
       </c>
       <c r="G43" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="H43" t="s">
         <v>4</v>
@@ -16488,87 +16491,87 @@
         <v>72</v>
       </c>
     </row>
-    <row r="44" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A44" s="2"/>
       <c r="E44" s="10"/>
     </row>
-    <row r="45" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A45" s="2"/>
       <c r="E45" s="10"/>
     </row>
-    <row r="46" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A46" s="2"/>
       <c r="E46" s="10"/>
     </row>
-    <row r="47" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A47" s="2"/>
       <c r="E47" s="10"/>
     </row>
-    <row r="48" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A48" s="2"/>
       <c r="E48" s="10"/>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A49" s="2"/>
       <c r="E49" s="10"/>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A50" s="2"/>
       <c r="E50" s="10"/>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A51" s="2"/>
       <c r="E51" s="10"/>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A52" s="2"/>
       <c r="E52" s="10"/>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A53" s="2"/>
       <c r="E53" s="10"/>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A54" s="2"/>
       <c r="E54" s="10"/>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A55" s="2"/>
       <c r="E55" s="10"/>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A56" s="2"/>
       <c r="E56" s="10"/>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A57" s="2"/>
       <c r="E57" s="10"/>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A58" s="2"/>
       <c r="E58" s="10"/>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A59" s="2"/>
       <c r="E59" s="10"/>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A60" s="2"/>
       <c r="E60" s="10"/>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A61" s="2"/>
       <c r="E61" s="10"/>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A62" s="2"/>
       <c r="E62" s="10"/>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A63" s="2"/>
       <c r="E63" s="10"/>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A64" s="2"/>
       <c r="E64" s="10"/>
     </row>
